--- a/artfynd/A 58132-2021 artfynd.xlsx
+++ b/artfynd/A 58132-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 58132-2021 artfynd.xlsx
+++ b/artfynd/A 58132-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54644366</v>
+        <v>54644332</v>
       </c>
       <c r="B2" t="n">
-        <v>93021</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96313</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,12 +700,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(With.) Myrin</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -722,14 +717,14 @@
       <c r="L2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ölen, Vrm</t>
+          <t>Ölen., Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>472935.7336795565</v>
+        <v>472903</v>
       </c>
       <c r="R2" t="n">
-        <v>6565319.892048256</v>
+        <v>6565286</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,21 +754,11 @@
           <t>2015-07-21</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-07-21</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -790,7 +775,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>5 klibbalar</t>
+          <t>klibbalar och stubbe</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -808,15 +793,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54644350</v>
+        <v>54644336</v>
       </c>
       <c r="B3" t="n">
-        <v>93021</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96313</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -838,12 +818,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(With.) Myrin</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -859,10 +839,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>472927.8355580505</v>
+        <v>472900</v>
       </c>
       <c r="R3" t="n">
-        <v>6565290.77376609</v>
+        <v>6565302</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,21 +872,11 @@
           <t>2015-07-21</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-07-21</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -923,7 +893,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>klibbal</t>
+          <t>sten och klibbal</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -941,15 +911,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54644376</v>
+        <v>54644350</v>
       </c>
       <c r="B4" t="n">
-        <v>93021</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96313</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -971,7 +936,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(With.) Myrin</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,10 +957,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>472943.0571249434</v>
+        <v>472928</v>
       </c>
       <c r="R4" t="n">
-        <v>6565340.313145504</v>
+        <v>6565291</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,19 +990,9 @@
           <t>2015-07-21</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-07-21</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1077,12 +1032,7 @@
         <v>54644358</v>
       </c>
       <c r="B5" t="n">
-        <v>93021</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96313</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1054,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(With.) Myrin</t>
+          <t>(L. ex Dicks.) Myrin</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1125,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>472933.5991357398</v>
+        <v>472934</v>
       </c>
       <c r="R5" t="n">
-        <v>6565308.135106556</v>
+        <v>6565308</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1158,19 +1108,9 @@
           <t>2015-07-21</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-07-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1204,6 +1144,242 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>54644366</v>
+      </c>
+      <c r="B6" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>530</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ölen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>472936</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6565320</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2015-07-21</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2015-07-21</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>5 klibbalar</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>54644376</v>
+      </c>
+      <c r="B7" t="n">
+        <v>96313</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>530</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Hårklomossa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dichelyma capillaceum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L. ex Dicks.) Myrin</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ölen, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>472943</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6565340</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Degerfors</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2015-07-21</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2015-07-21</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>sjöstrand</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>klibbal</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Per Darell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Per Darell, Liselott Evasdotter</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58132-2021 artfynd.xlsx
+++ b/artfynd/A 58132-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -790,6 +795,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54644332</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -908,6 +918,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54644336</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1026,6 +1041,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54644350</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1144,6 +1164,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54644358</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1262,6 +1287,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54644366</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1380,8 +1410,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/54644376</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>